--- a/data/trans_bre/P57_AF_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P57_AF_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 10,97</t>
+          <t>-1,68; 11,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 7,49</t>
+          <t>-5,41; 8,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 5,84</t>
+          <t>-7,28; 5,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 18,56</t>
+          <t>-3,73; 18,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 22,69</t>
+          <t>-3,02; 25,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 14,38</t>
+          <t>-9,24; 16,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 8,81</t>
+          <t>-10,09; 7,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 63,49</t>
+          <t>-9,48; 60,95</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 4,34</t>
+          <t>-6,61; 4,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 13,47</t>
+          <t>2,56; 13,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 3,39</t>
+          <t>-6,48; 3,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,58; -3,17</t>
+          <t>-29,46; -3,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 7,57</t>
+          <t>-10,93; 7,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 24,79</t>
+          <t>4,2; 25,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 4,64</t>
+          <t>-8,39; 4,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,47; -5,95</t>
+          <t>-53,44; -7,09</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 4,06</t>
+          <t>-6,08; 4,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 5,03</t>
+          <t>-5,56; 5,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 4,51</t>
+          <t>-5,91; 4,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 4,41</t>
+          <t>-8,14; 3,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 6,94</t>
+          <t>-9,55; 8,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 8,03</t>
+          <t>-8,11; 8,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 6,54</t>
+          <t>-7,78; 5,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 8,33</t>
+          <t>-13,57; 7,41</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 5,2</t>
+          <t>-7,3; 5,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 14,89</t>
+          <t>3,35; 14,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 5,65</t>
+          <t>-3,64; 6,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 40,11</t>
+          <t>-2,69; 37,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 8,76</t>
+          <t>-11,15; 9,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 24,81</t>
+          <t>4,98; 24,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 7,78</t>
+          <t>-4,6; 8,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 215,23</t>
+          <t>-4,75; 185,75</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 8,81</t>
+          <t>-3,78; 9,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 16,14</t>
+          <t>2,72; 16,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 10,57</t>
+          <t>-1,36; 10,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 6,66</t>
+          <t>-2,68; 7,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 14,65</t>
+          <t>-5,49; 16,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 29,4</t>
+          <t>4,23; 29,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 14,82</t>
+          <t>-1,8; 15,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 11,38</t>
+          <t>-4,12; 12,32</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 4,5</t>
+          <t>-9,48; 5,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 10,55</t>
+          <t>-4,22; 10,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 14,78</t>
+          <t>2,1; 15,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 29,96</t>
+          <t>-2,85; 28,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 7,06</t>
+          <t>-13,39; 8,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 16,87</t>
+          <t>-5,85; 17,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 21,83</t>
+          <t>2,8; 23,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 51,18</t>
+          <t>-4,56; 48,07</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 5,13</t>
+          <t>-10,06; 5,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 4,98</t>
+          <t>-9,92; 5,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 12,32</t>
+          <t>0,01; 12,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 8,34</t>
+          <t>-2,03; 9,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 7,6</t>
+          <t>-13,24; 8,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 7,5</t>
+          <t>-13,51; 8,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 16,66</t>
+          <t>-0,01; 16,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 13,12</t>
+          <t>-2,93; 14,21</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,99</t>
+          <t>-1,92; 3,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,32</t>
+          <t>2,54; 7,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,3</t>
+          <t>0,08; 4,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 19,88</t>
+          <t>0,3; 19,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,02</t>
+          <t>-3,07; 5,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,94; 12,06</t>
+          <t>3,96; 12,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,11; 5,9</t>
+          <t>0,1; 5,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 47,02</t>
+          <t>0,67; 43,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_AF_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P57_AF_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,42</t>
+          <t>7,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 11,8</t>
+          <t>-1,38; 11,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 8,37</t>
+          <t>-6,0; 7,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 5,33</t>
+          <t>-7,31; 5,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 18,29</t>
+          <t>-3,24; 18,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 25,45</t>
+          <t>-2,69; 22,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 16,19</t>
+          <t>-10,41; 14,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 7,95</t>
+          <t>-9,96; 8,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 60,95</t>
+          <t>-7,46; 56,0</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-12,46</t>
+          <t>-5,53</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-23,31%</t>
+          <t>-10,09%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 4,39</t>
+          <t>-6,9; 3,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 13,66</t>
+          <t>2,55; 14,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 3,42</t>
+          <t>-6,92; 3,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,46; -3,19</t>
+          <t>-13,08; 2,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 7,84</t>
+          <t>-11,48; 6,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 25,16</t>
+          <t>4,47; 25,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 4,72</t>
+          <t>-8,92; 4,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,44; -7,09</t>
+          <t>-22,15; 5,45</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>-2,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,98%</t>
+          <t>-3,53%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 4,92</t>
+          <t>-6,31; 4,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 5,21</t>
+          <t>-5,44; 5,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 4,16</t>
+          <t>-5,64; 4,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 3,98</t>
+          <t>-7,32; 2,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 8,51</t>
+          <t>-10,02; 8,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 8,38</t>
+          <t>-7,91; 8,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 5,89</t>
+          <t>-7,44; 6,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 7,41</t>
+          <t>-11,83; 5,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,19</t>
+          <t>2,27</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 5,33</t>
+          <t>-6,75; 5,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 14,73</t>
+          <t>3,36; 14,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 6,69</t>
+          <t>-3,94; 5,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 37,87</t>
+          <t>-2,49; 7,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 9,17</t>
+          <t>-10,55; 9,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 24,09</t>
+          <t>5,12; 23,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 8,97</t>
+          <t>-4,97; 8,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 185,75</t>
+          <t>-4,11; 13,8</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 9,54</t>
+          <t>-3,66; 9,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 16,2</t>
+          <t>3,24; 16,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 10,76</t>
+          <t>-0,99; 10,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 7,23</t>
+          <t>-3,55; 6,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 16,43</t>
+          <t>-5,49; 15,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 29,18</t>
+          <t>5,35; 30,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 15,08</t>
+          <t>-0,94; 15,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 12,32</t>
+          <t>-5,55; 10,77</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,03</t>
+          <t>-1,13</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>-1,81%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 5,21</t>
+          <t>-10,0; 4,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 10,82</t>
+          <t>-4,0; 11,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 15,77</t>
+          <t>2,27; 15,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 28,29</t>
+          <t>-6,46; 3,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 8,22</t>
+          <t>-14,02; 6,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 17,21</t>
+          <t>-5,66; 17,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,8; 23,15</t>
+          <t>3,02; 23,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 48,07</t>
+          <t>-10,04; 6,74</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,21</t>
+          <t>3,05</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 5,81</t>
+          <t>-10,22; 5,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 5,77</t>
+          <t>-10,7; 5,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 12,43</t>
+          <t>-1,13; 11,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 9,0</t>
+          <t>-2,95; 8,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 8,67</t>
+          <t>-13,49; 8,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 8,52</t>
+          <t>-14,17; 7,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 16,66</t>
+          <t>-1,22; 16,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 14,21</t>
+          <t>-4,02; 13,69</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,43</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,05</t>
+          <t>-1,87; 3,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,36</t>
+          <t>2,64; 7,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,17</t>
+          <t>0,05; 4,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 19,56</t>
+          <t>-1,28; 3,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 5,14</t>
+          <t>-3,0; 5,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,96; 12,19</t>
+          <t>4,16; 12,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 5,7</t>
+          <t>0,07; 5,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 43,49</t>
+          <t>-2,16; 6,37</t>
         </is>
       </c>
     </row>
